--- a/spectral_slope/TS9純音.xlsx
+++ b/spectral_slope/TS9純音.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\recording_application\spectral_slope\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75E5056-5740-4AA2-A572-FD17EBA0B606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE8C65A-75C2-48C1-B01D-85F93A02D297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
